--- a/suivi_taches.xlsx
+++ b/suivi_taches.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3972A92F-A5E7-4C93-A14C-7A2862F0A95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1F06A3-8DD5-40DB-86A2-DE521F596086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Suivi" sheetId="1" r:id="rId1"/>
@@ -924,7 +924,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -956,19 +956,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1041,8 +1035,8 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0ADF688A-8753-492E-AE81-51C2ACD7EDE1}" name="Table2" displayName="Table2" ref="A1:M100" totalsRowShown="0" dataDxfId="13">
   <autoFilter ref="A1:M100" xr:uid="{0ADF688A-8753-492E-AE81-51C2ACD7EDE1}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M98">
-    <sortCondition ref="C1:C98"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M100">
+    <sortCondition ref="C1:C100"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{4F006A25-C195-4CE0-BFA1-A12D1BA0DCFF}" name="Catégorie" dataDxfId="12"/>
@@ -1386,20 +1380,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M100"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.8984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.69921875" customWidth="1"/>
+    <col min="2" max="2" width="44.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.75" customWidth="1"/>
     <col min="4" max="4" width="10.5" customWidth="1"/>
-    <col min="5" max="5" width="15.69921875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.69921875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.69921875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="51.19921875" customWidth="1"/>
-    <col min="9" max="13" width="35.69921875" customWidth="1"/>
+    <col min="5" max="5" width="15.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.75" style="2" customWidth="1"/>
+    <col min="7" max="7" width="10.75" style="2" customWidth="1"/>
+    <col min="8" max="8" width="51.25" customWidth="1"/>
+    <col min="9" max="13" width="35.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1440,7 +1434,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>48</v>
       </c>
@@ -1471,7 +1465,7 @@
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>127</v>
       </c>
@@ -1508,7 +1502,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>127</v>
       </c>
@@ -1545,7 +1539,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>222</v>
       </c>
@@ -1574,7 +1568,7 @@
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>127</v>
       </c>
@@ -1603,7 +1597,7 @@
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>48</v>
       </c>
@@ -1634,7 +1628,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>48</v>
       </c>
@@ -1665,7 +1659,7 @@
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>48</v>
       </c>
@@ -1690,7 +1684,7 @@
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>48</v>
       </c>
@@ -1717,7 +1711,7 @@
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
@@ -1756,7 +1750,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -1793,7 +1787,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
@@ -1830,7 +1824,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>51</v>
       </c>
@@ -1869,7 +1863,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>57</v>
       </c>
@@ -1908,7 +1902,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>57</v>
       </c>
@@ -1947,7 +1941,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>23</v>
       </c>
@@ -1976,7 +1970,7 @@
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>23</v>
       </c>
@@ -2015,7 +2009,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>23</v>
       </c>
@@ -2042,7 +2036,7 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>125</v>
       </c>
@@ -2069,7 +2063,7 @@
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>127</v>
       </c>
@@ -2098,7 +2092,7 @@
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>48</v>
       </c>
@@ -2129,7 +2123,7 @@
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>23</v>
       </c>
@@ -2158,7 +2152,7 @@
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>23</v>
       </c>
@@ -2197,7 +2191,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>127</v>
       </c>
@@ -2226,129 +2220,127 @@
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>223</v>
+        <v>126</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="C26" s="4">
-        <v>46234</v>
-      </c>
-      <c r="D26" s="5">
-        <v>46234</v>
-      </c>
-      <c r="E26" s="6"/>
+        <v>46244</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="F26" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>225</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" spans="1:13" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>101</v>
+        <v>48</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>72</v>
       </c>
       <c r="C27" s="4">
-        <v>46235</v>
-      </c>
-      <c r="D27" s="3"/>
+        <v>46248</v>
+      </c>
+      <c r="D27" s="5">
+        <v>46357</v>
+      </c>
       <c r="E27" s="6" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="I27" s="3"/>
+        <v>237</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>138</v>
+      </c>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>100</v>
+        <v>224</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>223</v>
       </c>
       <c r="C28" s="4">
-        <v>46244</v>
-      </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="6" t="s">
-        <v>13</v>
-      </c>
+        <v>46249</v>
+      </c>
+      <c r="D28" s="5"/>
+      <c r="E28" s="6"/>
       <c r="F28" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="I28" s="3"/>
+        <v>245</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>225</v>
+      </c>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" ht="63" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>72</v>
+        <v>23</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="C29" s="4">
-        <v>46248</v>
-      </c>
-      <c r="D29" s="5">
-        <v>46357</v>
-      </c>
+        <v>46249</v>
+      </c>
+      <c r="D29" s="3"/>
       <c r="E29" s="6" t="s">
-        <v>13</v>
+        <v>132</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>138</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
     </row>
-    <row r="30" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>48</v>
       </c>
@@ -2381,7 +2373,7 @@
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
     </row>
-    <row r="31" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>123</v>
       </c>
@@ -2410,7 +2402,7 @@
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>52</v>
       </c>
@@ -2439,7 +2431,7 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
     </row>
-    <row r="33" spans="1:13" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>23</v>
       </c>
@@ -2470,7 +2462,7 @@
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>23</v>
       </c>
@@ -2499,7 +2491,7 @@
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
     </row>
-    <row r="35" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>123</v>
       </c>
@@ -2530,7 +2522,7 @@
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>127</v>
       </c>
@@ -2559,7 +2551,7 @@
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
     </row>
-    <row r="37" spans="1:13" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>127</v>
       </c>
@@ -2590,7 +2582,7 @@
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>48</v>
       </c>
@@ -2621,7 +2613,7 @@
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>127</v>
       </c>
@@ -2658,7 +2650,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>127</v>
       </c>
@@ -2687,7 +2679,7 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>127</v>
       </c>
@@ -2716,7 +2708,7 @@
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
     </row>
-    <row r="42" spans="1:13" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>11</v>
       </c>
@@ -2755,7 +2747,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>23</v>
       </c>
@@ -2784,7 +2776,7 @@
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>48</v>
       </c>
@@ -2817,7 +2809,7 @@
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>48</v>
       </c>
@@ -2848,7 +2840,7 @@
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
@@ -2877,7 +2869,7 @@
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>127</v>
       </c>
@@ -2906,11 +2898,11 @@
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="10" t="s">
         <v>262</v>
       </c>
       <c r="C48" s="4">
@@ -2933,57 +2925,53 @@
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>84</v>
+        <v>271</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>270</v>
       </c>
       <c r="C49" s="4">
-        <v>46251</v>
-      </c>
-      <c r="D49" s="5"/>
-      <c r="E49" s="6" t="s">
-        <v>141</v>
-      </c>
+        <v>46249</v>
+      </c>
+      <c r="D49" s="3"/>
+      <c r="E49" s="6"/>
       <c r="F49" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>238</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H49" s="7"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
     </row>
-    <row r="50" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="C50" s="4">
-        <v>46264</v>
-      </c>
-      <c r="D50" s="3"/>
+        <v>46251</v>
+      </c>
+      <c r="D50" s="5"/>
       <c r="E50" s="6" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
@@ -2991,12 +2979,12 @@
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C51" s="4">
         <v>46264</v>
@@ -3009,10 +2997,10 @@
         <v>25</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>152</v>
+        <v>228</v>
       </c>
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
@@ -3020,12 +3008,12 @@
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C52" s="4">
         <v>46264</v>
@@ -3049,28 +3037,28 @@
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
     </row>
-    <row r="53" spans="1:13" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="C53" s="4">
         <v>46264</v>
       </c>
-      <c r="D53" s="5"/>
+      <c r="D53" s="3"/>
       <c r="E53" s="6" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>195</v>
+        <v>152</v>
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
@@ -3078,26 +3066,28 @@
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B54" s="10" t="s">
-        <v>226</v>
+        <v>48</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="C54" s="4">
         <v>46264</v>
       </c>
-      <c r="D54" s="3"/>
-      <c r="E54" s="6"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="6" t="s">
+        <v>142</v>
+      </c>
       <c r="F54" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>246</v>
+        <v>195</v>
       </c>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
@@ -3105,28 +3095,26 @@
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
     </row>
-    <row r="55" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>110</v>
+        <v>122</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>226</v>
       </c>
       <c r="C55" s="4">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="D55" s="3"/>
-      <c r="E55" s="6" t="s">
-        <v>142</v>
-      </c>
+      <c r="E55" s="6"/>
       <c r="F55" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>197</v>
+        <v>246</v>
       </c>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
@@ -3134,19 +3122,19 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
     </row>
-    <row r="56" spans="1:13" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="C56" s="4">
         <v>46265</v>
       </c>
       <c r="D56" s="3"/>
       <c r="E56" s="6" t="s">
-        <v>13</v>
+        <v>142</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>14</v>
@@ -3155,22 +3143,20 @@
         <v>28</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>207</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
     </row>
-    <row r="57" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B57" s="10" t="s">
-        <v>205</v>
+        <v>23</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="C57" s="4">
         <v>46265</v>
@@ -3182,65 +3168,67 @@
       <c r="F57" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G57" s="6"/>
+      <c r="G57" s="6" t="s">
+        <v>28</v>
+      </c>
       <c r="H57" s="7" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="J57" s="3"/>
       <c r="K57" s="3"/>
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B58" s="12" t="s">
-        <v>249</v>
+        <v>48</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>205</v>
       </c>
       <c r="C58" s="4">
         <v>46265</v>
       </c>
       <c r="D58" s="3"/>
-      <c r="E58" s="6"/>
+      <c r="E58" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="F58" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G58" s="6"/>
       <c r="H58" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="I58" s="3"/>
+        <v>242</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>220</v>
+      </c>
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>114</v>
+        <v>52</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>249</v>
       </c>
       <c r="C59" s="4">
-        <v>46266</v>
-      </c>
-      <c r="D59" s="5"/>
-      <c r="E59" s="6" t="s">
-        <v>53</v>
-      </c>
+        <v>46265</v>
+      </c>
+      <c r="D59" s="3"/>
+      <c r="E59" s="6"/>
       <c r="F59" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>28</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G59" s="6"/>
       <c r="H59" s="7" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="I59" s="3"/>
       <c r="J59" s="3"/>
@@ -3248,51 +3236,41 @@
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
     </row>
-    <row r="60" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B60" s="10" t="s">
-        <v>43</v>
+        <v>48</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>114</v>
       </c>
       <c r="C60" s="4">
         <v>46266</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="6" t="s">
-        <v>132</v>
+        <v>53</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+        <v>236</v>
+      </c>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3"/>
+      <c r="K60" s="3"/>
+      <c r="L60" s="3"/>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B61" s="9" t="s">
-        <v>68</v>
+      <c r="B61" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="C61" s="4">
         <v>46266</v>
@@ -3310,162 +3288,172 @@
       <c r="H61" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="I61" s="3"/>
-      <c r="J61" s="3"/>
-      <c r="K61" s="3"/>
-      <c r="L61" s="3"/>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="1:13" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="I61" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M61" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C62" s="4">
         <v>46266</v>
       </c>
-      <c r="D62" s="3"/>
-      <c r="E62" s="8" t="s">
-        <v>13</v>
+      <c r="D62" s="5"/>
+      <c r="E62" s="6" t="s">
+        <v>132</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>28</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>208</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="I62" s="3"/>
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" ht="63" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>123</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C63" s="4">
         <v>46266</v>
       </c>
       <c r="D63" s="3"/>
-      <c r="E63" s="6" t="s">
+      <c r="E63" s="8" t="s">
         <v>13</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="I63" s="3"/>
+        <v>260</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>208</v>
+      </c>
       <c r="J63" s="3"/>
       <c r="K63" s="3"/>
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B64" s="10" t="s">
-        <v>27</v>
+        <v>123</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="C64" s="4">
         <v>46266</v>
       </c>
       <c r="D64" s="3"/>
       <c r="E64" s="6" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L64" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M64" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B65" s="9" t="s">
-        <v>261</v>
+        <v>23</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="C65" s="4">
         <v>46266</v>
       </c>
-      <c r="D65" s="5"/>
+      <c r="D65" s="3"/>
       <c r="E65" s="6" t="s">
-        <v>13</v>
+        <v>132</v>
       </c>
       <c r="F65" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>133</v>
+        <v>15</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="I65" s="3"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3"/>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+        <v>191</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M65" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>77</v>
+        <v>261</v>
       </c>
       <c r="C66" s="4">
         <v>46266</v>
       </c>
-      <c r="D66" s="3"/>
+      <c r="D66" s="5"/>
       <c r="E66" s="6" t="s">
-        <v>142</v>
+        <v>13</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>146</v>
+        <v>244</v>
       </c>
       <c r="I66" s="3"/>
       <c r="J66" s="3"/>
@@ -3473,12 +3461,12 @@
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C67" s="4">
         <v>46266</v>
@@ -3502,12 +3490,12 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C68" s="4">
         <v>46266</v>
@@ -3531,12 +3519,12 @@
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C69" s="4">
         <v>46266</v>
@@ -3560,12 +3548,12 @@
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="C70" s="4">
         <v>46266</v>
@@ -3581,7 +3569,7 @@
         <v>49</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>211</v>
+        <v>146</v>
       </c>
       <c r="I70" s="3"/>
       <c r="J70" s="3"/>
@@ -3589,28 +3577,28 @@
       <c r="L70" s="3"/>
       <c r="M70" s="3"/>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>127</v>
+        <v>48</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C71" s="4">
         <v>46266</v>
       </c>
       <c r="D71" s="3"/>
       <c r="E71" s="6" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="F71" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>154</v>
+        <v>211</v>
       </c>
       <c r="I71" s="3"/>
       <c r="J71" s="3"/>
@@ -3618,12 +3606,12 @@
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B72" s="10" t="s">
-        <v>35</v>
+      <c r="B72" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="C72" s="4">
         <v>46266</v>
@@ -3641,129 +3629,129 @@
       <c r="H72" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I72" s="3"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3"/>
+      <c r="L72" s="3"/>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B73" s="9" t="s">
-        <v>117</v>
+        <v>127</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="C73" s="4">
         <v>46266</v>
       </c>
       <c r="D73" s="3"/>
       <c r="E73" s="6" t="s">
-        <v>13</v>
+        <v>132</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G73" s="6" t="s">
         <v>28</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="J73" s="3"/>
-      <c r="K73" s="3"/>
-      <c r="L73" s="3"/>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L73" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M73" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B74" s="10" t="s">
-        <v>188</v>
+      <c r="B74" s="9" t="s">
+        <v>117</v>
       </c>
       <c r="C74" s="4">
         <v>46266</v>
       </c>
-      <c r="D74" s="4">
-        <v>46388</v>
-      </c>
+      <c r="D74" s="3"/>
       <c r="E74" s="6" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>183</v>
+        <v>28</v>
       </c>
       <c r="H74" s="7" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K74" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L74" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M74" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+      <c r="J74" s="3"/>
+      <c r="K74" s="3"/>
+      <c r="L74" s="3"/>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B75" s="9" t="s">
-        <v>93</v>
+        <v>124</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>188</v>
       </c>
       <c r="C75" s="4">
         <v>46266</v>
       </c>
-      <c r="D75" s="3"/>
+      <c r="D75" s="4">
+        <v>46388</v>
+      </c>
       <c r="E75" s="6" t="s">
-        <v>13</v>
+        <v>132</v>
       </c>
       <c r="F75" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="I75" s="3"/>
-      <c r="J75" s="3"/>
-      <c r="K75" s="3"/>
-      <c r="L75" s="3"/>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L75" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M75" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C76" s="4">
         <v>46266</v>
@@ -3776,10 +3764,10 @@
         <v>14</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>28</v>
+        <v>172</v>
       </c>
       <c r="H76" s="7" t="s">
-        <v>174</v>
+        <v>264</v>
       </c>
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
@@ -3787,12 +3775,12 @@
       <c r="L76" s="3"/>
       <c r="M76" s="3"/>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C77" s="4">
         <v>46266</v>
@@ -3802,13 +3790,13 @@
         <v>13</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I77" s="3"/>
       <c r="J77" s="3"/>
@@ -3816,12 +3804,12 @@
       <c r="L77" s="3"/>
       <c r="M77" s="3"/>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="C78" s="4">
         <v>46266</v>
@@ -3831,13 +3819,13 @@
         <v>13</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>40</v>
       </c>
       <c r="H78" s="7" t="s">
-        <v>265</v>
+        <v>175</v>
       </c>
       <c r="I78" s="3"/>
       <c r="J78" s="3"/>
@@ -3845,12 +3833,12 @@
       <c r="L78" s="3"/>
       <c r="M78" s="3"/>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C79" s="4">
         <v>46266</v>
@@ -3863,10 +3851,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>176</v>
+        <v>265</v>
       </c>
       <c r="I79" s="3"/>
       <c r="J79" s="3"/>
@@ -3874,12 +3862,12 @@
       <c r="L79" s="3"/>
       <c r="M79" s="3"/>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C80" s="4">
         <v>46266</v>
@@ -3889,13 +3877,13 @@
         <v>13</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H80" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I80" s="3"/>
       <c r="J80" s="3"/>
@@ -3903,12 +3891,12 @@
       <c r="L80" s="3"/>
       <c r="M80" s="3"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C81" s="4">
         <v>46266</v>
@@ -3924,7 +3912,7 @@
         <v>40</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I81" s="3"/>
       <c r="J81" s="3"/>
@@ -3932,12 +3920,12 @@
       <c r="L81" s="3"/>
       <c r="M81" s="3"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="C82" s="4">
         <v>46266</v>
@@ -3947,13 +3935,13 @@
         <v>13</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="H82" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
@@ -3961,26 +3949,28 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
     </row>
-    <row r="83" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="B83" s="10" t="s">
-        <v>247</v>
+        <v>56</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>113</v>
       </c>
       <c r="C83" s="4">
-        <v>46269</v>
+        <v>46266</v>
       </c>
       <c r="D83" s="3"/>
       <c r="E83" s="6" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G83" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>28</v>
+      </c>
       <c r="H83" s="7" t="s">
-        <v>248</v>
+        <v>179</v>
       </c>
       <c r="I83" s="3"/>
       <c r="J83" s="3"/>
@@ -3988,15 +3978,15 @@
       <c r="L83" s="3"/>
       <c r="M83" s="3"/>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>129</v>
+        <v>251</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>50</v>
+        <v>247</v>
       </c>
       <c r="C84" s="4">
-        <v>46295</v>
+        <v>46269</v>
       </c>
       <c r="D84" s="3"/>
       <c r="E84" s="6" t="s">
@@ -4005,79 +3995,57 @@
       <c r="F84" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G84" s="6" t="s">
-        <v>183</v>
-      </c>
+      <c r="G84" s="6"/>
       <c r="H84" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I84" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J84" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K84" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L84" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M84" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+      <c r="I84" s="3"/>
+      <c r="J84" s="3"/>
+      <c r="K84" s="3"/>
+      <c r="L84" s="3"/>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>52</v>
+        <v>268</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>55</v>
+        <v>267</v>
       </c>
       <c r="C85" s="4">
-        <v>46296</v>
+        <v>46280</v>
       </c>
       <c r="D85" s="3"/>
-      <c r="E85" s="6" t="s">
-        <v>53</v>
-      </c>
+      <c r="E85" s="6"/>
       <c r="F85" s="6" t="s">
         <v>25</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>183</v>
+        <v>49</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I85" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J85" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K85" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L85" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M85" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+        <v>269</v>
+      </c>
+      <c r="I85" s="3"/>
+      <c r="J85" s="3"/>
+      <c r="K85" s="3"/>
+      <c r="L85" s="3"/>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>23</v>
+        <v>129</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>181</v>
+        <v>50</v>
       </c>
       <c r="C86" s="4">
-        <v>46388</v>
+        <v>46295</v>
       </c>
       <c r="D86" s="3"/>
-      <c r="E86" s="6"/>
+      <c r="E86" s="6" t="s">
+        <v>139</v>
+      </c>
       <c r="F86" s="6" t="s">
         <v>25</v>
       </c>
@@ -4085,16 +4053,16 @@
         <v>183</v>
       </c>
       <c r="H86" s="7" t="s">
-        <v>199</v>
+        <v>16</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="J86" s="3" t="s">
         <v>16</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>204</v>
+        <v>16</v>
       </c>
       <c r="L86" s="3" t="s">
         <v>16</v>
@@ -4103,15 +4071,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>52</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C87" s="4">
-        <v>46388</v>
+        <v>46296</v>
       </c>
       <c r="D87" s="3"/>
       <c r="E87" s="6" t="s">
@@ -4124,16 +4092,16 @@
         <v>183</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>200</v>
+        <v>16</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>192</v>
+        <v>16</v>
       </c>
       <c r="J87" s="3" t="s">
         <v>16</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>190</v>
+        <v>16</v>
       </c>
       <c r="L87" s="3" t="s">
         <v>16</v>
@@ -4142,96 +4110,86 @@
         <v>16</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B88" s="10" t="s">
-        <v>33</v>
+        <v>128</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>86</v>
       </c>
       <c r="C88" s="4">
-        <v>46478</v>
+        <v>46310</v>
       </c>
       <c r="D88" s="3"/>
       <c r="E88" s="6" t="s">
-        <v>171</v>
+        <v>53</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>183</v>
+        <v>218</v>
       </c>
       <c r="H88" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="I88" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J88" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K88" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="L88" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M88" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+      <c r="I88" s="3"/>
+      <c r="J88" s="3"/>
+      <c r="K88" s="3"/>
+      <c r="L88" s="3"/>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C89" s="4">
-        <v>46508</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>190</v>
-      </c>
+        <v>46310</v>
+      </c>
+      <c r="D89" s="3"/>
       <c r="E89" s="6" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H89" s="7"/>
+        <v>218</v>
+      </c>
+      <c r="H89" s="7" t="s">
+        <v>219</v>
+      </c>
       <c r="I89" s="3"/>
       <c r="J89" s="3"/>
       <c r="K89" s="3"/>
       <c r="L89" s="3"/>
       <c r="M89" s="3"/>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>48</v>
+        <v>128</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="C90" s="4"/>
-      <c r="D90" s="5">
-        <v>46357</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="C90" s="4">
+        <v>46310</v>
+      </c>
+      <c r="D90" s="3"/>
       <c r="E90" s="6" t="s">
-        <v>139</v>
+        <v>53</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>133</v>
+        <v>218</v>
       </c>
       <c r="H90" s="7" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
@@ -4239,99 +4197,113 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B91" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C91" s="4"/>
-      <c r="D91" s="5">
-        <v>46387</v>
-      </c>
-      <c r="E91" s="6" t="s">
-        <v>213</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B91" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C91" s="4">
+        <v>46388</v>
+      </c>
+      <c r="D91" s="3"/>
+      <c r="E91" s="6"/>
       <c r="F91" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>49</v>
+        <v>183</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="I91" s="3"/>
-      <c r="J91" s="3"/>
-      <c r="K91" s="3"/>
-      <c r="L91" s="3"/>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>124</v>
+        <v>52</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="C92" s="4"/>
+        <v>54</v>
+      </c>
+      <c r="C92" s="4">
+        <v>46388</v>
+      </c>
       <c r="D92" s="3"/>
       <c r="E92" s="6" t="s">
-        <v>132</v>
+        <v>53</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G92" s="6" t="s">
         <v>183</v>
       </c>
       <c r="H92" s="7" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>16</v>
+        <v>192</v>
       </c>
       <c r="J92" s="3" t="s">
         <v>16</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>42</v>
+        <v>190</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="M92" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B93" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="C93" s="4"/>
+        <v>124</v>
+      </c>
+      <c r="B93" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C93" s="4">
+        <v>46478</v>
+      </c>
       <c r="D93" s="3"/>
-      <c r="E93" s="6"/>
+      <c r="E93" s="6" t="s">
+        <v>171</v>
+      </c>
       <c r="F93" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G93" s="6" t="s">
         <v>183</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>216</v>
+        <v>266</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="J93" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K93" s="3" t="s">
-        <v>24</v>
+      <c r="K93" s="7" t="s">
+        <v>202</v>
       </c>
       <c r="L93" s="3" t="s">
         <v>16</v>
@@ -4340,98 +4312,86 @@
         <v>16</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B94" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C94" s="4"/>
-      <c r="D94" s="3"/>
+        <v>122</v>
+      </c>
+      <c r="B94" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C94" s="4">
+        <v>46508</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>190</v>
+      </c>
       <c r="E94" s="6" t="s">
-        <v>217</v>
+        <v>13</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>183</v>
+        <v>20</v>
       </c>
       <c r="H94" s="7"/>
-      <c r="I94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I94" s="3"/>
+      <c r="J94" s="3"/>
+      <c r="K94" s="3"/>
+      <c r="L94" s="3"/>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B95" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
+      </c>
+      <c r="B95" s="12" t="s">
+        <v>120</v>
       </c>
       <c r="C95" s="4"/>
-      <c r="D95" s="3"/>
+      <c r="D95" s="5">
+        <v>46357</v>
+      </c>
       <c r="E95" s="6" t="s">
-        <v>217</v>
+        <v>139</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="H95" s="7"/>
-      <c r="I95" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J95" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K95" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L95" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M95" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+      <c r="H95" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="I95" s="3"/>
+      <c r="J95" s="3"/>
+      <c r="K95" s="3"/>
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B96" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C96" s="4">
-        <v>46310</v>
-      </c>
-      <c r="D96" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="B96" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C96" s="4"/>
+      <c r="D96" s="5">
+        <v>46387</v>
+      </c>
       <c r="E96" s="6" t="s">
-        <v>53</v>
+        <v>213</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>218</v>
+        <v>49</v>
       </c>
       <c r="H96" s="7" t="s">
-        <v>219</v>
+        <v>153</v>
       </c>
       <c r="I96" s="3"/>
       <c r="J96" s="3"/>
@@ -4439,115 +4399,147 @@
       <c r="L96" s="3"/>
       <c r="M96" s="3"/>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C97" s="4">
-        <v>46310</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="B97" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="C97" s="4"/>
       <c r="D97" s="3"/>
       <c r="E97" s="6" t="s">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="H97" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="I97" s="3"/>
-      <c r="J97" s="3"/>
-      <c r="K97" s="3"/>
-      <c r="L97" s="3"/>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+        <v>215</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K97" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L97" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M97" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C98" s="4">
-        <v>46310</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C98" s="4"/>
       <c r="D98" s="3"/>
-      <c r="E98" s="6" t="s">
-        <v>53</v>
-      </c>
+      <c r="E98" s="6"/>
       <c r="F98" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="H98" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="I98" s="3"/>
-      <c r="J98" s="3"/>
-      <c r="K98" s="3"/>
-      <c r="L98" s="3"/>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+        <v>216</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L98" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M98" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B99" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="C99" s="4">
-        <v>46280</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C99" s="4"/>
       <c r="D99" s="3"/>
-      <c r="E99" s="6"/>
+      <c r="E99" s="6" t="s">
+        <v>217</v>
+      </c>
       <c r="F99" s="6" t="s">
         <v>25</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H99" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="I99" s="3"/>
-      <c r="J99" s="3"/>
-      <c r="K99" s="3"/>
-      <c r="L99" s="3"/>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+      <c r="H99" s="7"/>
+      <c r="I99" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J99" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K99" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L99" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M99" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B100" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="C100" s="4">
-        <v>46249</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C100" s="4"/>
       <c r="D100" s="3"/>
-      <c r="E100" s="6"/>
+      <c r="E100" s="6" t="s">
+        <v>217</v>
+      </c>
       <c r="F100" s="6" t="s">
         <v>25</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>15</v>
+        <v>183</v>
       </c>
       <c r="H100" s="7"/>
-      <c r="I100" s="3"/>
-      <c r="J100" s="3"/>
-      <c r="K100" s="3"/>
-      <c r="L100" s="3"/>
-      <c r="M100" s="3"/>
+      <c r="I100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
